--- a/Convert_from_xlsx_to_Json/table_normalization/education-table12.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table12.xlsx
@@ -415,7 +415,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
@@ -446,14 +446,8 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -496,59 +490,62 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal 3" xfId="2"/>
@@ -1119,7 +1116,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1127,70 +1124,70 @@
       <c r="A2" s="7"/>
     </row>
     <row r="3" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="32" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="32" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
     </row>
     <row r="4" spans="1:15" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="H4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="48" t="s">
+      <c r="K4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="48" t="s">
+      <c r="L4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="M4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="O4" s="49" t="s">
+      <c r="O4" s="46" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1216,7 +1213,7 @@
       <c r="G5" s="9">
         <v>470830</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="20">
         <v>1119800</v>
       </c>
       <c r="I5" s="9">
@@ -1237,7 +1234,7 @@
       <c r="N5" s="9">
         <v>192140</v>
       </c>
-      <c r="O5" s="22">
+      <c r="O5" s="20">
         <v>575700</v>
       </c>
     </row>
@@ -1263,7 +1260,7 @@
       <c r="G6" s="11">
         <v>489590</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="21">
         <v>1101700</v>
       </c>
       <c r="I6" s="11">
@@ -1284,7 +1281,7 @@
       <c r="N6" s="11">
         <v>206840</v>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="21">
         <v>578800</v>
       </c>
     </row>
@@ -1310,7 +1307,7 @@
       <c r="G7" s="13">
         <v>2220</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="22">
         <v>150900</v>
       </c>
       <c r="I7" s="13">
@@ -1331,175 +1328,175 @@
       <c r="N7" s="13">
         <v>1290</v>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="22">
         <v>119200</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>770980</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>30720</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>28780</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>161690</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>800</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <v>545370</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="23">
         <v>1538300</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="14">
         <v>506050</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="14">
         <v>23790</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="14">
         <v>20780</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="14">
         <v>123660</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="14">
         <v>610</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="14">
         <v>246850</v>
       </c>
-      <c r="O8" s="25">
+      <c r="O8" s="23">
         <v>921700</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="50"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="15">
         <v>318190</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="15">
         <v>5130</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="15">
         <v>13510</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="15">
         <v>120370</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <v>590</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="15">
         <v>307000</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="24">
         <v>764800</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="15">
         <v>206520</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="15">
         <v>3600</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="15">
         <v>10280</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="15">
         <v>95090</v>
       </c>
-      <c r="M10" s="17">
+      <c r="M10" s="15">
         <v>460</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="15">
         <v>140920</v>
       </c>
-      <c r="O10" s="26">
+      <c r="O10" s="24">
         <v>456900</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="43"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
     </row>
     <row r="12" spans="1:15" s="2" customFormat="1" ht="18.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="44"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="43"/>
+      <c r="L12" s="43"/>
+      <c r="M12" s="43"/>
+      <c r="N12" s="43"/>
+      <c r="O12" s="43"/>
     </row>
     <row r="13" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
     </row>
     <row r="14" spans="1:15" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14"/>
@@ -1908,72 +1905,72 @@
       <c r="O35"/>
     </row>
     <row r="36" spans="1:31" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="35"/>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
+      <c r="A36" s="45"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="45"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="45"/>
+      <c r="O36" s="45"/>
     </row>
     <row r="37" spans="1:31" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="18"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
     </row>
     <row r="38" spans="1:31" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="19"/>
-      <c r="M38" s="19"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="28"/>
+      <c r="A38" s="40"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="26"/>
     </row>
     <row r="39" spans="1:31" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="28"/>
+      <c r="A39" s="40"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+      <c r="L39" s="17"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="26"/>
     </row>
     <row r="40" spans="1:31" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="38"/>
@@ -1993,55 +1990,55 @@
       <c r="O40" s="38"/>
     </row>
     <row r="41" spans="1:31" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="29"/>
+      <c r="A41" s="39"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="39"/>
+      <c r="H41" s="39"/>
+      <c r="I41" s="39"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="27"/>
     </row>
     <row r="42" spans="1:31" s="6" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="39"/>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="39"/>
+      <c r="A42" s="36"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="36"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="36"/>
     </row>
     <row r="43" spans="1:31" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="40"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="40"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="40"/>
-      <c r="K43" s="40"/>
-      <c r="L43" s="40"/>
-      <c r="M43" s="40"/>
-      <c r="N43" s="40"/>
-      <c r="O43" s="40"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+      <c r="M43" s="37"/>
+      <c r="N43" s="37"/>
+      <c r="O43" s="37"/>
     </row>
     <row r="44" spans="1:31" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="38"/>
@@ -2059,27 +2056,32 @@
       <c r="M44" s="38"/>
       <c r="N44" s="38"/>
       <c r="O44" s="38"/>
-      <c r="P44" s="31"/>
+      <c r="P44" s="29"/>
     </row>
     <row r="45" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="20"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
-      <c r="J45" s="21"/>
-      <c r="K45" s="21"/>
-      <c r="L45" s="21"/>
-      <c r="M45" s="21"/>
-      <c r="N45" s="21"/>
-      <c r="O45" s="21"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="I3:O3"/>
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="A36:O36"/>
     <mergeCell ref="A42:O42"/>
     <mergeCell ref="A43:O43"/>
     <mergeCell ref="A44:O44"/>
@@ -2088,11 +2090,6 @@
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A40:O40"/>
     <mergeCell ref="A41:I41"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="A36:O36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="55" orientation="landscape"/>
